--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125696021</v>
+        <v>125696206</v>
       </c>
       <c r="B2" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577852</v>
+        <v>577932</v>
       </c>
       <c r="R2" t="n">
-        <v>6398936</v>
+        <v>6399025</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125696238</v>
+        <v>125696089</v>
       </c>
       <c r="B3" t="n">
-        <v>110139</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,31 +795,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577782</v>
+        <v>577880</v>
       </c>
       <c r="R3" t="n">
-        <v>6398955</v>
+        <v>6398956</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,18 +869,12 @@
           <t>2025-06-04</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Få på marken</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125696089</v>
+        <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,35 +904,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577880</v>
+        <v>577836</v>
       </c>
       <c r="R4" t="n">
-        <v>6398956</v>
+        <v>6398930</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,12 +974,18 @@
           <t>2025-06-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Få på marken</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,37 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125696053</v>
+        <v>125696186</v>
       </c>
       <c r="B5" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1067,14 +1047,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 24839, ankarsrums säteri, Sm</t>
+          <t>A 24839, Ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>577852</v>
       </c>
       <c r="R5" t="n">
-        <v>6398936</v>
+        <v>6399076</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1133,15 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125695971</v>
+        <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110139</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577836</v>
+        <v>577782</v>
       </c>
       <c r="R6" t="n">
-        <v>6398930</v>
+        <v>6398955</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,15 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125696196</v>
+        <v>125696021</v>
       </c>
       <c r="B7" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,35 +1235,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1304,10 +1273,10 @@
         <v>577852</v>
       </c>
       <c r="R7" t="n">
-        <v>6399076</v>
+        <v>6398936</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,6 +1314,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1363,37 +1333,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125696186</v>
+        <v>125696196</v>
       </c>
       <c r="B8" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1477,15 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125696206</v>
+        <v>125696053</v>
       </c>
       <c r="B9" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,14 +1485,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 24839, Ankarsrums säteri, Sm</t>
+          <t>A 24839, ankarsrums säteri, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577932</v>
+        <v>577852</v>
       </c>
       <c r="R9" t="n">
-        <v>6399025</v>
+        <v>6398936</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>110194</v>
+        <v>110201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110194</v>
+        <v>110201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>125696021</v>
       </c>
       <c r="B7" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125696206</v>
       </c>
       <c r="B2" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>125696089</v>
       </c>
       <c r="B3" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>110201</v>
+        <v>110204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>125696186</v>
       </c>
       <c r="B5" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110201</v>
+        <v>110204</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>125696021</v>
       </c>
       <c r="B7" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125696196</v>
       </c>
       <c r="B8" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>125696053</v>
       </c>
       <c r="B9" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>110204</v>
+        <v>110208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110204</v>
+        <v>110208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>125696021</v>
       </c>
       <c r="B7" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>110208</v>
+        <v>110209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110208</v>
+        <v>110209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125696206</v>
       </c>
       <c r="B2" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>125696089</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>110209</v>
+        <v>110211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>125696186</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110209</v>
+        <v>110211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>125696021</v>
       </c>
       <c r="B7" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125696196</v>
       </c>
       <c r="B8" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>125696053</v>
       </c>
       <c r="B9" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>110211</v>
+        <v>110213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110211</v>
+        <v>110213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>125696021</v>
       </c>
       <c r="B7" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>110213</v>
+        <v>110217</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110213</v>
+        <v>110217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>125696021</v>
       </c>
       <c r="B7" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125696206</v>
       </c>
       <c r="B2" t="n">
-        <v>57934</v>
+        <v>57938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>125696089</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>110217</v>
+        <v>110230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>125696186</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110217</v>
+        <v>110230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>125696021</v>
       </c>
       <c r="B7" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>125696196</v>
       </c>
       <c r="B8" t="n">
-        <v>57934</v>
+        <v>57938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>125696053</v>
       </c>
       <c r="B9" t="n">
-        <v>57934</v>
+        <v>57938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>125695971</v>
       </c>
       <c r="B4" t="n">
-        <v>110230</v>
+        <v>110233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>125696238</v>
       </c>
       <c r="B6" t="n">
-        <v>110230</v>
+        <v>110233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110568</v>
+        <v>110573</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110568</v>
+        <v>110573</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>129079128</v>
       </c>
       <c r="B13" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110573</v>
+        <v>110576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110573</v>
+        <v>110576</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,45 +1864,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B13" t="n">
-        <v>92852</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R13" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,13 +1945,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1973,42 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>92855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R14" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,17 +2058,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110576</v>
+        <v>110586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110576</v>
+        <v>110586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,42 +1864,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>92862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1907,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R13" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,17 +1948,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1974,45 +1973,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B14" t="n">
-        <v>92855</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2020,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R14" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,13 +2054,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110586</v>
+        <v>110593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110586</v>
+        <v>110593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,45 +1864,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B13" t="n">
-        <v>92862</v>
+        <v>57722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R13" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,13 +1945,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1973,42 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R14" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,17 +2058,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110593</v>
+        <v>110595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110593</v>
+        <v>110595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,42 +1864,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B13" t="n">
-        <v>57722</v>
+        <v>92871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1907,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R13" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,17 +1948,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1974,45 +1973,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2020,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R14" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,13 +2054,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110595</v>
+        <v>110621</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110595</v>
+        <v>110621</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,45 +1864,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B13" t="n">
-        <v>92871</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R13" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,13 +1945,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1973,42 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>92857</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R14" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,17 +2058,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110621</v>
+        <v>110623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110621</v>
+        <v>110623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,42 +1864,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>92858</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1907,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R13" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,17 +1948,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1974,45 +1973,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B14" t="n">
-        <v>92857</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2020,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R14" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,13 +2054,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110623</v>
+        <v>110624</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110623</v>
+        <v>110624</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,45 +1864,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B13" t="n">
-        <v>92858</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R13" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,13 +1945,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1973,42 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>92858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R14" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,17 +2058,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110624</v>
+        <v>110628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110624</v>
+        <v>110628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>129079128</v>
       </c>
       <c r="B14" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110628</v>
+        <v>110630</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110628</v>
+        <v>110630</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,42 +1864,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>92863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1907,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R13" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,17 +1948,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1974,45 +1973,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B14" t="n">
-        <v>92861</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2020,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R14" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,13 +2054,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110630</v>
+        <v>110634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110630</v>
+        <v>110634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>129079128</v>
       </c>
       <c r="B13" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110634</v>
+        <v>110644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110634</v>
+        <v>110644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>129079128</v>
       </c>
       <c r="B13" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1554,7 +1554,7 @@
         <v>129079150</v>
       </c>
       <c r="B10" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129079165</v>
       </c>
       <c r="B11" t="n">
-        <v>110644</v>
+        <v>110647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>129079189</v>
       </c>
       <c r="B12" t="n">
-        <v>110644</v>
+        <v>110647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,45 +1864,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B13" t="n">
-        <v>92868</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R13" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,13 +1945,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1973,42 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>92871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R14" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,17 +2058,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>129079220</v>
       </c>
       <c r="B15" t="n">
-        <v>92844</v>
+        <v>92847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1864,42 +1864,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B13" t="n">
-        <v>57724</v>
+        <v>92871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1907,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R13" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,17 +1948,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1974,45 +1973,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B14" t="n">
-        <v>92871</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2020,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R14" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,13 +2054,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24839-2025 artfynd.xlsx
+++ b/artfynd/A 24839-2025 artfynd.xlsx
@@ -1864,45 +1864,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129079128</v>
+        <v>129079247</v>
       </c>
       <c r="B13" t="n">
-        <v>92871</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577776</v>
+        <v>577791</v>
       </c>
       <c r="R13" t="n">
-        <v>6398957</v>
+        <v>6399004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,13 +1945,17 @@
           <t>2025-10-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1973,42 +1974,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129079247</v>
+        <v>129079128</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>92871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577791</v>
+        <v>577776</v>
       </c>
       <c r="R14" t="n">
-        <v>6399004</v>
+        <v>6398957</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,17 +2058,13 @@
           <t>2025-10-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
